--- a/表格模版/UPS(美洲).xlsx
+++ b/表格模版/UPS(美洲).xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28740" windowHeight="12300"/>
+    <workbookView windowWidth="21080" windowHeight="13540"/>
   </bookViews>
   <sheets>
     <sheet name="发票" sheetId="1" r:id="rId1"/>
@@ -1358,7 +1358,7 @@
       <c r="C4" s="6"/>
       <c r="D4" s="7">
         <f ca="1">TODAY()</f>
-        <v>45663</v>
+        <v>45924</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
@@ -1399,9 +1399,7 @@
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="6"/>
-      <c r="D6" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="D6" s="5"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
@@ -1415,7 +1413,9 @@
       <c r="O6" s="6"/>
     </row>
     <row r="7" spans="1:15">
-      <c r="A7" s="5"/>
+      <c r="A7" s="5" t="s">
+        <v>7</v>
+      </c>
       <c r="B7" s="8"/>
       <c r="C7" s="9"/>
       <c r="D7" s="5"/>

--- a/表格模版/UPS(美洲).xlsx
+++ b/表格模版/UPS(美洲).xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21080" windowHeight="13540"/>
+    <workbookView windowHeight="13420"/>
   </bookViews>
   <sheets>
     <sheet name="发票" sheetId="1" r:id="rId1"/>
@@ -106,7 +106,7 @@
     <numFmt numFmtId="178" formatCode="&quot;US$&quot;#,##0.00;&quot;-US$&quot;#,##0.00"/>
     <numFmt numFmtId="179" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="27">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -134,12 +134,6 @@
       <b/>
       <sz val="11"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
@@ -752,13 +746,16 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="12">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="12">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
@@ -767,126 +764,123 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="13">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="14">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="15">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="16">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="15">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="17">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="18">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="19">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="15">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="16">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="15">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="17">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="18">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="19">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -922,18 +916,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="11" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -945,11 +928,14 @@
     <xf numFmtId="178" fontId="4" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="4" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="51">
@@ -1358,7 +1344,7 @@
       <c r="C4" s="6"/>
       <c r="D4" s="7">
         <f ca="1">TODAY()</f>
-        <v>45924</v>
+        <v>45943</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
@@ -1482,10 +1468,10 @@
       <c r="E12" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="F12" s="23" t="s">
+      <c r="F12" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="G12" s="24" t="s">
+      <c r="G12" s="21" t="s">
         <v>14</v>
       </c>
       <c r="H12" s="16" t="s">
@@ -1494,41 +1480,41 @@
       <c r="I12" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="J12" s="25" t="s">
+      <c r="J12" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="K12" s="26" t="s">
+      <c r="K12" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="L12" s="26" t="s">
+      <c r="L12" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="M12" s="26" t="s">
+      <c r="M12" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="N12" s="26" t="s">
+      <c r="N12" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="O12" s="27" t="s">
+      <c r="O12" s="24" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="13" ht="90" customHeight="1" spans="1:15">
+    <row r="13" ht="82" customHeight="1" spans="1:15">
       <c r="A13" s="19"/>
-      <c r="B13" s="20"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="22"/>
-      <c r="J13" s="20"/>
-      <c r="K13" s="20"/>
-      <c r="L13" s="20"/>
-      <c r="M13" s="20"/>
-      <c r="N13" s="22"/>
-      <c r="O13" s="22"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="12">
